--- a/2. Báo cáo - giấy tờ/1. Báo cáo/Bàn giao/Bàn giao bảo hành VNSH03 VNET Aithings - 270926.xlsx
+++ b/2. Báo cáo - giấy tờ/1. Báo cáo/Bàn giao/Bàn giao bảo hành VNSH03 VNET Aithings - 270926.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\2. Báo cáo - giấy tờ\1. Báo cáo\Bàn giao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F5DED68-9FE3-49F4-9C81-68DFB718C4D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6043123E-AA80-405B-87AA-218F5F2EAE44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="59">
   <si>
     <t/>
   </si>
@@ -123,9 +123,6 @@
     <t>Website: https://vnetgps.vn/</t>
   </si>
   <si>
-    <t>Hôm nay ngày 08/09/2026, chúng tôi gồm:</t>
-  </si>
-  <si>
     <t>Công Ty TNHH Công Nghệ AITHINGS</t>
   </si>
   <si>
@@ -154,6 +151,57 @@
   </si>
   <si>
     <t>Địa chỉ: Tầng 04, Tòa nhà văn phòng Minori, 67A Trương Định, P. Trương Định, Q. Hai Bà Trưng, TP. Hà Nội</t>
+  </si>
+  <si>
+    <t>VNET861385071455938</t>
+  </si>
+  <si>
+    <t>Lỗi nguồn</t>
+  </si>
+  <si>
+    <t>VNET861385071486560</t>
+  </si>
+  <si>
+    <t>VNET861385071448487</t>
+  </si>
+  <si>
+    <t>VNET861385071545175</t>
+  </si>
+  <si>
+    <t>VNET861385071531415</t>
+  </si>
+  <si>
+    <t>VNET861385071461407</t>
+  </si>
+  <si>
+    <t>VNET861385071448313</t>
+  </si>
+  <si>
+    <t>VNET861385071455128</t>
+  </si>
+  <si>
+    <t>VNET861385071530888</t>
+  </si>
+  <si>
+    <t>VNET860879084183652</t>
+  </si>
+  <si>
+    <t>VNET860879084180864</t>
+  </si>
+  <si>
+    <t>VNET860879084182605</t>
+  </si>
+  <si>
+    <t>VNET861385071517976</t>
+  </si>
+  <si>
+    <t>VNET861385070624815</t>
+  </si>
+  <si>
+    <t>Hôm nay ngày 27/10/2026, chúng tôi gồm:</t>
+  </si>
+  <si>
+    <t>BOXCAM</t>
   </si>
 </sst>
 </file>
@@ -241,7 +289,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -260,20 +308,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -631,7 +670,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -646,25 +685,25 @@
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="C1" s="11"/>
-      <c r="D1" s="12" t="s">
+      <c r="C1" s="8"/>
+      <c r="D1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="12"/>
+      <c r="E1" s="9"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="8"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="7"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
@@ -674,10 +713,10 @@
         <v>30</v>
       </c>
       <c r="C3" s="4"/>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="8"/>
+      <c r="E3" s="7"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
@@ -693,17 +732,17 @@
     <row r="5" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4"/>
       <c r="B5" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="4"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="B6" s="12" t="s">
+      <c r="A6" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="B6" s="9" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="4"/>
@@ -716,27 +755,27 @@
       <c r="A7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="11"/>
-      <c r="D7" s="12" t="s">
+      <c r="C7" s="8"/>
+      <c r="D7" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="12"/>
+      <c r="E7" s="9"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12" t="s">
+      <c r="C8" s="9"/>
+      <c r="D8" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="E8" s="12"/>
+      <c r="E8" s="9"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
@@ -747,7 +786,7 @@
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E9" s="4"/>
     </row>
@@ -755,38 +794,38 @@
       <c r="A10" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10" s="11"/>
-      <c r="D10" s="12" t="s">
+      <c r="B10" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="8"/>
+      <c r="D10" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="12"/>
+      <c r="E10" s="9"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12" t="s">
+      <c r="B11" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="E11" s="12"/>
+      <c r="E11" s="9"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>17</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C12" s="4"/>
       <c r="D12" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E12" s="4"/>
     </row>
@@ -794,11 +833,11 @@
       <c r="A13" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14" t="s">
+      <c r="B13" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11" t="s">
         <v>20</v>
       </c>
       <c r="E13" s="4"/>
@@ -811,205 +850,289 @@
         <v>22</v>
       </c>
       <c r="C14" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>38</v>
+      <c r="E14" s="6" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="17"/>
-      <c r="B15" s="17"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="18"/>
+      <c r="A15" s="14">
+        <v>1</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E15" s="15"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="17"/>
-      <c r="B16" s="17"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="18"/>
+      <c r="A16" s="14">
+        <v>2</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E16" s="15"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="17"/>
-      <c r="B17" s="17"/>
-      <c r="C17" s="17"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="18"/>
+      <c r="A17" s="14">
+        <v>3</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E17" s="15"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="17"/>
-      <c r="B18" s="17"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="18"/>
+      <c r="A18" s="14">
+        <v>4</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="D18" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E18" s="15"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="17"/>
-      <c r="B19" s="17"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="18"/>
+      <c r="A19" s="14">
+        <v>5</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E19" s="15"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="17"/>
-      <c r="B20" s="17"/>
-      <c r="C20" s="17"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="18"/>
+      <c r="A20" s="14">
+        <v>6</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D20" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E20" s="15"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="17"/>
-      <c r="B21" s="17"/>
-      <c r="C21" s="17"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="18"/>
+      <c r="A21" s="14">
+        <v>7</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D21" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E21" s="15"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="17"/>
-      <c r="B22" s="17"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="18"/>
+      <c r="A22" s="14">
+        <v>8</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="D22" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E22" s="15"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="17"/>
-      <c r="B23" s="17"/>
-      <c r="C23" s="17"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="18"/>
+      <c r="A23" s="14">
+        <v>9</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="D23" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E23" s="15"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="17"/>
-      <c r="B24" s="17"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="18"/>
+      <c r="A24" s="14">
+        <v>10</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="D24" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E24" s="15"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="17"/>
-      <c r="B25" s="17"/>
-      <c r="C25" s="17"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="18"/>
+      <c r="A25" s="14">
+        <v>11</v>
+      </c>
+      <c r="B25" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C25" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="D25" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E25" s="15"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="17"/>
-      <c r="B26" s="17"/>
-      <c r="C26" s="17"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="18"/>
+      <c r="A26" s="14">
+        <v>12</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C26" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="D26" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E26" s="15"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="17"/>
-      <c r="B27" s="17"/>
-      <c r="C27" s="17"/>
-      <c r="D27" s="17"/>
-      <c r="E27" s="18"/>
+      <c r="A27" s="14">
+        <v>13</v>
+      </c>
+      <c r="B27" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C27" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="D27" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E27" s="15"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="17"/>
-      <c r="B28" s="17"/>
-      <c r="C28" s="17"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="18"/>
+      <c r="A28" s="14">
+        <v>14</v>
+      </c>
+      <c r="B28" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C28" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="D28" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E28" s="15"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="17"/>
-      <c r="B29" s="17"/>
-      <c r="C29" s="17"/>
-      <c r="D29" s="17"/>
-      <c r="E29" s="18"/>
+      <c r="A29" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="17"/>
-      <c r="B30" s="17"/>
-      <c r="C30" s="17"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="18"/>
+      <c r="A30" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="6"/>
-      <c r="B31" s="6"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="10"/>
-      <c r="E31" s="6"/>
+      <c r="A31" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="B31" s="12"/>
+      <c r="C31" s="12"/>
+      <c r="D31" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="E31" s="12"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="6"/>
-      <c r="B32" s="6"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="10"/>
-      <c r="E32" s="6"/>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="B33" s="12"/>
-      <c r="C33" s="12"/>
-      <c r="D33" s="12"/>
-      <c r="E33" s="12"/>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="B34" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="C34" s="12"/>
-      <c r="D34" s="12"/>
-      <c r="E34" s="12"/>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="B35" s="15"/>
-      <c r="C35" s="15"/>
-      <c r="D35" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="E35" s="15"/>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="16" t="s">
+      <c r="A32" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="B36" s="16"/>
-      <c r="C36" s="16"/>
-      <c r="D36" s="16" t="s">
+      <c r="B32" s="13"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="E36" s="16"/>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D41" s="13" t="s">
+      <c r="E32" s="13"/>
+    </row>
+    <row r="37" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D37" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="E41" s="13"/>
+      <c r="E37" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="D41:E41"/>
+    <mergeCell ref="D37:E37"/>
     <mergeCell ref="B8:E8"/>
     <mergeCell ref="B10:E10"/>
     <mergeCell ref="B11:E11"/>
     <mergeCell ref="B13:D13"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="A36:C36"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="D32:E32"/>
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="B7:E7"/>
-    <mergeCell ref="A33:E33"/>
-    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="A30:E30"/>
     <mergeCell ref="B2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
